--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 21:39</t>
+    <t xml:space="preserve">2026-09-10 00:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 00:47</t>
+    <t xml:space="preserve">2026-09-18 10:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 10:56</t>
+    <t xml:space="preserve">2026-09-23 14:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 14:16</t>
+    <t xml:space="preserve">2026-10-02 15:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
@@ -60,7 +60,7 @@
     <t xml:space="preserve">San Carlos</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ninhue</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:37</t>
+    <t xml:space="preserve">2026-10-04 09:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_e_mat_a_2019_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:58</t>
+    <t xml:space="preserve">2026-10-05 14:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
